--- a/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_43.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2788524.710881341</v>
+        <v>2781657.717932685</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10041900.99034356</v>
+        <v>10041900.99034355</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10041900.99034356</v>
+        <v>10041900.99034355</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162896221</v>
+        <v>286.4107162883329</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162896221</v>
+        <v>286.4107162883329</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14820953.30425012</v>
+        <v>14820953.30425013</v>
       </c>
     </row>
   </sheetData>
@@ -663,7 +663,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>33.06948099228313</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>135.3518862151736</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>147.2737972923793</v>
+        <v>282.6256835075529</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
@@ -909,7 +909,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>36.71585008894188</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -982,13 +982,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>26.7387362314949</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>385</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
@@ -1036,10 +1036,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>385</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>81.78289603071018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1222,13 +1222,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>308.4311513056531</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1258,10 +1258,10 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>385</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>218.9078536905206</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751175223</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1328,7 +1328,7 @@
         <v>240.445564079015</v>
       </c>
       <c r="P10" t="n">
-        <v>285.8567266822288</v>
+        <v>287.4478973282775</v>
       </c>
       <c r="Q10" t="n">
         <v>325.839266425598</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>236.6755817285639</v>
@@ -1428,7 +1428,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X11" t="n">
         <v>242.2818334606677</v>
@@ -1450,13 +1450,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S12" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T12" t="n">
         <v>55.35776521751382</v>
@@ -1620,10 +1620,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H14" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I14" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C15" t="n">
         <v>11.09991244551929</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1738,10 +1738,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U15" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856293</v>
       </c>
       <c r="V15" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
         <v>82.37314290982852</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S18" t="n">
         <v>116.5639999646113</v>
@@ -1984,7 +1984,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X18" t="n">
-        <v>69.86273944538755</v>
+        <v>150.372414784409</v>
       </c>
       <c r="Y18" t="n">
         <v>49.39139276613435</v>
@@ -2097,7 +2097,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T20" t="n">
         <v>236.6755817285639</v>
@@ -2200,10 +2200,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>547.2737972923793</v>
+        <v>436.872294727342</v>
       </c>
       <c r="S21" t="n">
         <v>116.5639999646113</v>
@@ -2212,7 +2212,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U21" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V21" t="n">
         <v>64.51066719152016</v>
@@ -2331,10 +2331,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>97.23431917176904</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
         <v>11.09991244551929</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>547.2737972923793</v>
+        <v>436.872294727342</v>
       </c>
       <c r="S24" t="n">
         <v>116.5639999646113</v>
@@ -2571,7 +2571,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>144.8481678023229</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>73.77767497096181</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S27" t="n">
         <v>116.5639999646113</v>
@@ -2808,7 +2808,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2853,7 +2853,7 @@
         <v>288.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>242.2818334606677</v>
+        <v>246.2472248460823</v>
       </c>
       <c r="Y29" t="n">
         <v>161.3174326828064</v>
@@ -2869,7 +2869,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>62.67776252544254</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S30" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T30" t="n">
         <v>55.35776521751382</v>
@@ -3042,7 +3042,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T32" t="n">
         <v>236.6755817285639</v>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3166,13 +3166,13 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X33" t="n">
-        <v>69.86273944538755</v>
+        <v>132.54050197083</v>
       </c>
       <c r="Y33" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T35" t="n">
         <v>236.6755817285639</v>
@@ -3349,19 +3349,19 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>195.551376634094</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
-        <v>134.5163324950501</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W36" t="n">
         <v>82.37314290982852</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T38" t="n">
         <v>236.6755817285639</v>
@@ -3589,10 +3589,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>86.93822665041522</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3640,10 +3640,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>69.86273944538755</v>
+        <v>132.54050197083</v>
       </c>
       <c r="Y39" t="n">
         <v>49.39139276613435</v>
@@ -3753,10 +3753,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H41" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I41" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3817,22 +3817,22 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>11.09991244551929</v>
+        <v>84.14143263308497</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>80.50967533902147</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>58.32868099228319</v>
+        <v>54.36328960686865</v>
       </c>
       <c r="F44" t="n">
         <v>54.88962870801186</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4069,10 +4069,10 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4108,10 +4108,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856293</v>
       </c>
       <c r="V45" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D2" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E2" t="n">
         <v>47.62490878641967</v>
@@ -4348,25 +4348,25 @@
         <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V2" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W2" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X2" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>722.3619790837812</v>
+        <v>585.6429020987573</v>
       </c>
       <c r="C3" t="n">
-        <v>722.3619790837812</v>
+        <v>585.6429020987573</v>
       </c>
       <c r="D3" t="n">
         <v>585.6429020987573</v>
@@ -4424,28 +4424,28 @@
         <v>1011.404879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>862.6434684666581</v>
+        <v>725.9243914816342</v>
       </c>
       <c r="S3" t="n">
-        <v>795.4071048660406</v>
+        <v>658.6880278810168</v>
       </c>
       <c r="T3" t="n">
-        <v>789.9952208079459</v>
+        <v>653.276143822922</v>
       </c>
       <c r="U3" t="n">
-        <v>789.7827362016966</v>
+        <v>653.0636592166727</v>
       </c>
       <c r="V3" t="n">
-        <v>775.1254966143025</v>
+        <v>638.4064196292786</v>
       </c>
       <c r="W3" t="n">
-        <v>742.4253522609404</v>
+        <v>605.7062752759165</v>
       </c>
       <c r="X3" t="n">
-        <v>722.3619790837812</v>
+        <v>585.6429020987573</v>
       </c>
       <c r="Y3" t="n">
-        <v>722.3619790837812</v>
+        <v>585.6429020987573</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>775.7097405151412</v>
+        <v>1022.260933153428</v>
       </c>
       <c r="C4" t="n">
-        <v>901.711746333577</v>
+        <v>1148.262938971864</v>
       </c>
       <c r="D4" t="n">
-        <v>1015.030890458577</v>
+        <v>1261.582083096864</v>
       </c>
       <c r="E4" t="n">
-        <v>1132.85979466999</v>
+        <v>1379.410987308277</v>
       </c>
       <c r="F4" t="n">
-        <v>1178.916259347549</v>
+        <v>1503.771959900212</v>
       </c>
       <c r="G4" t="n">
-        <v>1178.916259347549</v>
+        <v>1540</v>
       </c>
       <c r="H4" t="n">
-        <v>1178.916259347549</v>
+        <v>1540</v>
       </c>
       <c r="I4" t="n">
-        <v>1178.916259347549</v>
+        <v>1540</v>
       </c>
       <c r="J4" t="n">
         <v>1540</v>
@@ -4512,19 +4512,19 @@
         <v>30.8</v>
       </c>
       <c r="U4" t="n">
-        <v>30.8</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="V4" t="n">
-        <v>229.621392885946</v>
+        <v>476.1725855242326</v>
       </c>
       <c r="W4" t="n">
-        <v>401.5123111456234</v>
+        <v>648.0635037839101</v>
       </c>
       <c r="X4" t="n">
-        <v>552.5431021698168</v>
+        <v>799.0942948081035</v>
       </c>
       <c r="Y4" t="n">
-        <v>663.9524028488491</v>
+        <v>910.5035954871358</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D5" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E5" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G5" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H5" t="n">
         <v>30.8</v>
@@ -4585,25 +4585,25 @@
         <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="F6" t="n">
-        <v>30.8</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="G6" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H6" t="n">
         <v>30.8</v>
@@ -4661,28 +4661,28 @@
         <v>1011.404879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>622.5159909842129</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S6" t="n">
-        <v>555.2796273835954</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T6" t="n">
-        <v>549.8677433255007</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U6" t="n">
-        <v>549.6552587192514</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V6" t="n">
-        <v>534.9980191318573</v>
+        <v>775.1254966143025</v>
       </c>
       <c r="W6" t="n">
-        <v>502.2978747784952</v>
+        <v>742.4253522609404</v>
       </c>
       <c r="X6" t="n">
-        <v>113.4089858896062</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="Y6" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1022.260933153428</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="C7" t="n">
-        <v>1148.262938971864</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="D7" t="n">
-        <v>1261.582083096864</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="E7" t="n">
-        <v>1379.410987308277</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="F7" t="n">
-        <v>1503.771959900212</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="G7" t="n">
-        <v>1540</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="H7" t="n">
-        <v>1540</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="I7" t="n">
-        <v>1540</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="J7" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
       </c>
       <c r="L7" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M7" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O7" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P7" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>277.3511926382866</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>476.1725855242326</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W7" t="n">
-        <v>648.0635037839101</v>
+        <v>873.3894380368879</v>
       </c>
       <c r="X7" t="n">
-        <v>799.0942948081035</v>
+        <v>1024.420229061081</v>
       </c>
       <c r="Y7" t="n">
-        <v>910.5035954871358</v>
+        <v>1068.55182541068</v>
       </c>
     </row>
     <row r="8">
@@ -4795,19 +4795,19 @@
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="K8" t="n">
+        <v>411.9499999999999</v>
+      </c>
+      <c r="L8" t="n">
         <v>793.0999999999999</v>
       </c>
-      <c r="L8" t="n">
-        <v>1158.85</v>
-      </c>
       <c r="M8" t="n">
-        <v>1158.85</v>
+        <v>793.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1540</v>
+        <v>1174.25</v>
       </c>
       <c r="O8" t="n">
         <v>1540</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="E9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="F9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="G9" t="n">
-        <v>30.8</v>
+        <v>585.6429020987573</v>
       </c>
       <c r="H9" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="I9" t="n">
         <v>30.8</v>
@@ -4901,25 +4901,25 @@
         <v>1037.471008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>648.582120073203</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T9" t="n">
-        <v>427.463075941364</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U9" t="n">
-        <v>427.2505913351147</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>412.5933517477206</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>379.8932073943585</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>775.7097405151412</v>
+        <v>947.896520609007</v>
       </c>
       <c r="C10" t="n">
-        <v>901.711746333577</v>
+        <v>947.896520609007</v>
       </c>
       <c r="D10" t="n">
-        <v>901.711746333577</v>
+        <v>947.896520609007</v>
       </c>
       <c r="E10" t="n">
-        <v>901.711746333577</v>
+        <v>1065.72542482042</v>
       </c>
       <c r="F10" t="n">
-        <v>901.711746333577</v>
+        <v>1149.350535904526</v>
       </c>
       <c r="G10" t="n">
-        <v>901.711746333577</v>
+        <v>1149.350535904526</v>
       </c>
       <c r="H10" t="n">
-        <v>1068.551825410687</v>
+        <v>1318.867121063924</v>
       </c>
       <c r="I10" t="n">
-        <v>1068.551825410687</v>
+        <v>1540.000000000007</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063139</v>
+        <v>1540.000000000007</v>
       </c>
       <c r="K10" t="n">
         <v>1540.000000000007</v>
       </c>
       <c r="L10" t="n">
-        <v>1516.214517012351</v>
+        <v>1517.821760089146</v>
       </c>
       <c r="M10" t="n">
-        <v>1394.364404484523</v>
+        <v>1395.971647561318</v>
       </c>
       <c r="N10" t="n">
-        <v>1221.450187038377</v>
+        <v>1223.057430115171</v>
       </c>
       <c r="O10" t="n">
-        <v>978.5758798878566</v>
+        <v>980.1831229646514</v>
       </c>
       <c r="P10" t="n">
-        <v>689.8317115219688</v>
+        <v>689.8317115219468</v>
       </c>
       <c r="Q10" t="n">
-        <v>360.7011393749001</v>
+        <v>360.701139374878</v>
       </c>
       <c r="R10" t="n">
-        <v>30.8</v>
+        <v>30.7999999999779</v>
       </c>
       <c r="S10" t="n">
         <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>30.8</v>
+        <v>218.8756791588049</v>
       </c>
       <c r="U10" t="n">
-        <v>30.8</v>
+        <v>465.4268717970915</v>
       </c>
       <c r="V10" t="n">
-        <v>229.621392885946</v>
+        <v>664.2482646830374</v>
       </c>
       <c r="W10" t="n">
-        <v>401.5123111456234</v>
+        <v>836.1391829427148</v>
       </c>
       <c r="X10" t="n">
-        <v>552.5431021698168</v>
+        <v>836.1391829427148</v>
       </c>
       <c r="Y10" t="n">
-        <v>663.9524028488491</v>
+        <v>836.1391829427148</v>
       </c>
     </row>
     <row r="11">
@@ -5035,7 +5035,7 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>618.3311712710652</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L11" t="n">
         <v>1171.741171271065</v>
@@ -5059,16 +5059,16 @@
         <v>2236</v>
       </c>
       <c r="S11" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W11" t="n">
         <v>970.4091539265823</v>
@@ -5087,16 +5087,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C12" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D12" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="E12" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F12" t="n">
         <v>44.72</v>
@@ -5135,28 +5135,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S12" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T12" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U12" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V12" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W12" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X12" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y12" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="13">
@@ -5263,7 +5263,7 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
@@ -5272,22 +5272,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>989.4391130376558</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L14" t="n">
-        <v>989.4391130376558</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M14" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="N14" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="O14" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P14" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
         <v>44.72</v>
@@ -5381,19 +5381,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5509,13 +5509,13 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>989.4391130376558</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L17" t="n">
-        <v>1542.849113037656</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M17" t="n">
-        <v>2053.697941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="N17" t="n">
         <v>2236</v>
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119.2429040110725</v>
+        <v>391.4553531635761</v>
       </c>
       <c r="C18" t="n">
-        <v>108.0308712378206</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D18" t="n">
-        <v>108.0308712378206</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E18" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F18" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G18" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H18" t="n">
         <v>44.72</v>
@@ -5609,28 +5609,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S18" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T18" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U18" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V18" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W18" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X18" t="n">
-        <v>204.0388125085078</v>
+        <v>476.2512616610114</v>
       </c>
       <c r="Y18" t="n">
-        <v>154.1485167851397</v>
+        <v>426.3609659376434</v>
       </c>
     </row>
     <row r="19">
@@ -5719,49 +5719,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C20" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H20" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I20" t="n">
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>179.7320762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>733.1420762183976</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L20" t="n">
-        <v>733.1420762183976</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M20" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N20" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="O20" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P20" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5770,25 +5770,25 @@
         <v>2236</v>
       </c>
       <c r="S20" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y20" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="21">
@@ -5843,16 +5843,16 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R21" t="n">
-        <v>647.3506049216877</v>
+        <v>584.0397336838671</v>
       </c>
       <c r="S21" t="n">
-        <v>529.6091908160197</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T21" t="n">
-        <v>473.6922562528744</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U21" t="n">
         <v>359.6638499037541</v>
@@ -5974,28 +5974,28 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I23" t="n">
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>64.92117127106526</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>618.3311712710653</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L23" t="n">
-        <v>618.3311712710653</v>
+        <v>1129.18</v>
       </c>
       <c r="M23" t="n">
         <v>1129.18</v>
       </c>
       <c r="N23" t="n">
-        <v>1129.18</v>
+        <v>1682.59</v>
       </c>
       <c r="O23" t="n">
-        <v>1682.59</v>
+        <v>2236</v>
       </c>
       <c r="P23" t="n">
         <v>2236</v>
@@ -6080,31 +6080,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R24" t="n">
-        <v>647.3506049216877</v>
+        <v>584.0397336838671</v>
       </c>
       <c r="S24" t="n">
-        <v>529.6091908160197</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T24" t="n">
-        <v>473.6922562528744</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U24" t="n">
-        <v>422.9747211415747</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V24" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W24" t="n">
-        <v>274.6072361907174</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X24" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y24" t="n">
-        <v>154.1485167851397</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="25">
@@ -6114,16 +6114,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D25" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E25" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F25" t="n">
         <v>1153.55685638681</v>
@@ -6174,16 +6174,16 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W25" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="26">
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C26" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D26" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E26" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F26" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G26" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H26" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I26" t="n">
         <v>44.72</v>
@@ -6220,49 +6220,49 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>618.3311712710653</v>
+        <v>1286.552076218397</v>
       </c>
       <c r="M26" t="n">
-        <v>1129.18</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N26" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O26" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P26" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
       </c>
       <c r="R26" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S26" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T26" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U26" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V26" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W26" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X26" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y26" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="27">
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>119.2429040110725</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C27" t="n">
         <v>44.72</v>
@@ -6320,28 +6320,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S27" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T27" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U27" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V27" t="n">
-        <v>711.3477845844836</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W27" t="n">
-        <v>628.142589726071</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X27" t="n">
-        <v>557.5741660438614</v>
+        <v>494.2632948060406</v>
       </c>
       <c r="Y27" t="n">
-        <v>507.6838703204934</v>
+        <v>444.3729990826726</v>
       </c>
     </row>
     <row r="28">
@@ -6430,49 +6430,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C29" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D29" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E29" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F29" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G29" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H29" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
       </c>
       <c r="J29" t="n">
-        <v>436.0291130376557</v>
+        <v>64.92117127106515</v>
       </c>
       <c r="K29" t="n">
-        <v>436.0291130376557</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L29" t="n">
-        <v>436.0291130376557</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M29" t="n">
-        <v>946.8779417665908</v>
+        <v>1682.59</v>
       </c>
       <c r="N29" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="O29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6496,10 +6496,10 @@
         <v>974.4145997704354</v>
       </c>
       <c r="X29" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y29" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="G30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="H30" t="n">
         <v>44.72</v>
@@ -6557,28 +6557,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S30" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T30" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U30" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V30" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W30" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X30" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y30" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="31">
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C32" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D32" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E32" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F32" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G32" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H32" t="n">
         <v>44.72</v>
@@ -6691,25 +6691,25 @@
         <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>64.92117127106515</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>618.3311712710652</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L32" t="n">
-        <v>1171.741171271065</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M32" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N32" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O32" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P32" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6718,25 +6718,25 @@
         <v>2236</v>
       </c>
       <c r="S32" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T32" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U32" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V32" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W32" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X32" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y32" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C33" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="D33" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="E33" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="F33" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="G33" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="H33" t="n">
         <v>44.72</v>
@@ -6809,13 +6809,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W33" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X33" t="n">
-        <v>204.0388125085078</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y33" t="n">
-        <v>154.1485167851397</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="34">
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
@@ -6931,22 +6931,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>989.4391130376558</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L35" t="n">
-        <v>1542.849113037656</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="M35" t="n">
-        <v>2053.697941766591</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N35" t="n">
-        <v>2053.697941766591</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O35" t="n">
-        <v>2236</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6955,25 +6955,25 @@
         <v>2236</v>
       </c>
       <c r="S35" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>402.0654643105373</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C36" t="n">
-        <v>390.8534315372855</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D36" t="n">
-        <v>390.8534315372855</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E36" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F36" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G36" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H36" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I36" t="n">
         <v>44.72</v>
@@ -7043,16 +7043,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>640.6349913485949</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>557.4297964901822</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>486.8613728079725</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y36" t="n">
-        <v>436.9710770846045</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="37">
@@ -7141,46 +7141,46 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C38" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D38" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E38" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F38" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>44.72</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L38" t="n">
-        <v>179.7320762183977</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M38" t="n">
-        <v>690.5809049473327</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N38" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O38" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
         <v>1797.400904947332</v>
@@ -7192,25 +7192,25 @@
         <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y38" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="39">
@@ -7220,19 +7220,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
         <v>44.72</v>
@@ -7283,13 +7283,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7314,16 +7314,16 @@
         <v>1161.267639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H40" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I40" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K40" t="n">
         <v>1921.561060958496</v>
@@ -7396,31 +7396,31 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>64.92117127106515</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K41" t="n">
-        <v>618.3311712710652</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L41" t="n">
-        <v>1171.741171271065</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M41" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N41" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7460,19 +7460,19 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>461.5662247731743</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D42" t="n">
-        <v>461.5662247731743</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E42" t="n">
-        <v>380.2433203903244</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F42" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G42" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H42" t="n">
         <v>44.72</v>
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J43" t="n">
         <v>1860.696627021627</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="44">
@@ -7624,40 +7624,40 @@
         <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>137.1709049473328</v>
+        <v>44.72</v>
       </c>
       <c r="K44" t="n">
-        <v>690.5809049473327</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="L44" t="n">
-        <v>1243.990904947333</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M44" t="n">
-        <v>1243.990904947333</v>
+        <v>1129.18</v>
       </c>
       <c r="N44" t="n">
-        <v>1797.400904947332</v>
+        <v>1129.18</v>
       </c>
       <c r="O44" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P44" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I45" t="n">
         <v>44.72</v>
@@ -7751,19 +7751,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7827,16 +7827,16 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U46" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V46" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W46" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X46" t="n">
         <v>745.8791912947012</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
-        <v>384.9999999999999</v>
+        <v>385</v>
       </c>
       <c r="L8" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="M8" t="n">
         <v>544.2621276423173</v>
@@ -8453,7 +8453,7 @@
         <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409245</v>
+        <v>439.6923140185369</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
@@ -8678,10 +8678,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>184.14349316506</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8915,25 +8915,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
+        <v>184.14349316506</v>
+      </c>
+      <c r="L14" t="n">
         <v>559</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
-        <v>801.385149773304</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,7 +9152,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>184.14349316506</v>
       </c>
       <c r="L17" t="n">
         <v>559</v>
@@ -9161,7 +9161,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>661.3924512348951</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
         <v>70.24786957409245</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>171.4188408091283</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1036.248958069835</v>
+        <v>661.3924512348951</v>
       </c>
       <c r="O20" t="n">
         <v>70.24786957409245</v>
@@ -9407,7 +9407,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>55.44822975121687</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>559</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>141.1524110730752</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
         <v>172.8226843274854</v>
@@ -9863,25 +9863,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>184.1434931650601</v>
+        <v>300.1141042229713</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,13 +10097,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121676</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,13 +10112,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>370.3619737970638</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,16 +10334,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>55.44822975121676</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>559</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="L32" t="n">
         <v>559</v>
       </c>
       <c r="M32" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N32" t="n">
         <v>1036.248958069835</v>
@@ -10355,7 +10355,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,25 +10574,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>254.3913627391524</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,25 +10808,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
-        <v>1036.248958069835</v>
+        <v>734.3719802008218</v>
       </c>
       <c r="O38" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11045,13 +11045,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>55.44822975121676</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11066,7 +11066,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>128.4277587171436</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>20.40522350612653</v>
       </c>
       <c r="L44" t="n">
         <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.591170646026967</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23186,7 +23186,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.591170646048624</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3463644.874745413</v>
+        <v>3463644.874745414</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4313724.376969915</v>
+        <v>4313724.376969916</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5163803.879194415</v>
+        <v>5163803.879194417</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6013883.381418914</v>
+        <v>6013883.381418915</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6863962.883643412</v>
+        <v>6863962.883643413</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7714042.38586791</v>
+        <v>7714042.385867911</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8564121.888092408</v>
+        <v>8564121.88809241</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9414201.390316911</v>
+        <v>9414201.390316913</v>
       </c>
     </row>
     <row r="13">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11964439.89699043</v>
+        <v>11964439.89699044</v>
       </c>
     </row>
     <row r="16">
@@ -26275,7 +26275,7 @@
         <v>1353789.266154872</v>
       </c>
       <c r="D2" t="n">
-        <v>1353789.266154872</v>
+        <v>1353789.266154873</v>
       </c>
       <c r="E2" t="n">
         <v>1353830.31835754</v>
@@ -26287,22 +26287,22 @@
         <v>1353830.318357541</v>
       </c>
       <c r="H2" t="n">
+        <v>1353830.318357541</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1353830.318357541</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1353830.318357541</v>
+      </c>
+      <c r="K2" t="n">
         <v>1353830.31835754</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1353830.31835754</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1353830.31835754</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1353830.318357541</v>
       </c>
       <c r="L2" t="n">
         <v>1353830.31835754</v>
       </c>
       <c r="M2" t="n">
-        <v>1353830.31835754</v>
+        <v>1353830.318357541</v>
       </c>
       <c r="N2" t="n">
         <v>1353830.31835754</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416952</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114472</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116067</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>590319.5412553627</v>
+        <v>588803.6855670466</v>
       </c>
       <c r="C6" t="n">
-        <v>727897.521389177</v>
+        <v>726381.6657008614</v>
       </c>
       <c r="D6" t="n">
-        <v>729958.2933014928</v>
+        <v>728442.4376131776</v>
       </c>
       <c r="E6" t="n">
-        <v>406076.9151310049</v>
+        <v>404335.0653178972</v>
       </c>
       <c r="F6" t="n">
-        <v>749267.8104765093</v>
+        <v>747525.9606634014</v>
       </c>
       <c r="G6" t="n">
-        <v>751213.386944695</v>
+        <v>749471.5371315874</v>
       </c>
       <c r="H6" t="n">
-        <v>753161.6637619958</v>
+        <v>751419.8139488889</v>
       </c>
       <c r="I6" t="n">
-        <v>755112.6604053559</v>
+        <v>753370.8105922489</v>
       </c>
       <c r="J6" t="n">
-        <v>341546.3966069809</v>
+        <v>339804.546793874</v>
       </c>
       <c r="K6" t="n">
-        <v>759022.8923592013</v>
+        <v>757281.0425460926</v>
       </c>
       <c r="L6" t="n">
-        <v>760982.1679194599</v>
+        <v>759240.3181063524</v>
       </c>
       <c r="M6" t="n">
-        <v>701696.2438154394</v>
+        <v>699954.3940023324</v>
       </c>
       <c r="N6" t="n">
-        <v>764909.1408502926</v>
+        <v>763167.2910371855</v>
       </c>
       <c r="O6" t="n">
-        <v>486876.8801080311</v>
+        <v>485135.030294923</v>
       </c>
       <c r="P6" t="n">
-        <v>768847.4829590409</v>
+        <v>767105.6331459332</v>
       </c>
     </row>
   </sheetData>
@@ -26975,7 +26975,7 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
         <v>-0</v>
@@ -26987,13 +26987,13 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>350</v>
@@ -27036,7 +27036,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -27048,22 +27048,22 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -27094,7 +27094,7 @@
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -27442,7 +27442,7 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27518,7 +27518,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>212.585800682529</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27560,7 +27560,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>264.6481137848264</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27603,10 +27603,10 @@
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>320.9045374602253</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>281.6378527403057</v>
       </c>
       <c r="H4" t="n">
         <v>228.7711261016186</v>
@@ -27615,7 +27615,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
         <v>288.520773801143</v>
@@ -27648,7 +27648,7 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27761,13 +27761,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>312.897506106382</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27797,7 +27797,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>162.2737972923793</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27815,10 +27815,10 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>34.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>317.6084967354242</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27828,22 +27828,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>281.6378527403057</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>228.7711261016186</v>
@@ -27852,10 +27852,10 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27897,7 +27897,7 @@
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>332.0427228995621</v>
       </c>
     </row>
     <row r="8">
@@ -28001,13 +28001,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>17.3083845693742</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28037,10 +28037,10 @@
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>81.5639999646113</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>186.4499115269932</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28068,31 +28068,31 @@
         <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>358.8526651436071</v>
       </c>
       <c r="G10" t="n">
         <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
-        <v>397.2964585027402</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,13 +28116,13 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>362.3734797028778</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
@@ -28131,10 +28131,10 @@
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28195,7 +28195,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T11" t="n">
         <v>350</v>
@@ -28207,7 +28207,7 @@
         <v>350</v>
       </c>
       <c r="W11" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="X11" t="n">
         <v>350</v>
@@ -28229,13 +28229,13 @@
         <v>350</v>
       </c>
       <c r="D12" t="n">
-        <v>274.8961667101369</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
         <v>325.7395358750273</v>
@@ -28271,10 +28271,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T12" t="n">
         <v>350</v>
@@ -28399,10 +28399,10 @@
         <v>350</v>
       </c>
       <c r="H14" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I14" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C15" t="n">
         <v>350</v>
@@ -28469,7 +28469,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>279.9943346964701</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>339.6362423378769</v>
@@ -28517,10 +28517,10 @@
         <v>350</v>
       </c>
       <c r="U15" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="V15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>350</v>
@@ -28706,7 +28706,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>279.9943346964702</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -28715,7 +28715,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H18" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>217.1263858913485</v>
@@ -28745,7 +28745,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S18" t="n">
         <v>350</v>
@@ -28763,7 +28763,7 @@
         <v>350</v>
       </c>
       <c r="X18" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="Y18" t="n">
         <v>350</v>
@@ -28876,7 +28876,7 @@
         <v>350</v>
       </c>
       <c r="I20" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28906,7 +28906,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T20" t="n">
         <v>350</v>
@@ -28979,10 +28979,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="S21" t="n">
         <v>350</v>
@@ -28991,7 +28991,7 @@
         <v>350</v>
       </c>
       <c r="U21" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V21" t="n">
         <v>350</v>
@@ -29110,10 +29110,10 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I23" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29171,7 +29171,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="C24" t="n">
         <v>350</v>
@@ -29216,10 +29216,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="S24" t="n">
         <v>350</v>
@@ -29262,7 +29262,7 @@
         <v>350</v>
       </c>
       <c r="F25" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G25" t="n">
         <v>350</v>
@@ -29310,7 +29310,7 @@
         <v>350</v>
       </c>
       <c r="V25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="W25" t="n">
         <v>350</v>
@@ -29350,7 +29350,7 @@
         <v>350</v>
       </c>
       <c r="I26" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
         <v>350</v>
@@ -29408,10 +29408,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C27" t="n">
-        <v>287.3222374745575</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
@@ -29456,7 +29456,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S27" t="n">
         <v>350</v>
@@ -29587,7 +29587,7 @@
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29632,7 +29632,7 @@
         <v>350</v>
       </c>
       <c r="X29" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="Y29" t="n">
         <v>350</v>
@@ -29648,7 +29648,7 @@
         <v>350</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
@@ -29663,7 +29663,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
-        <v>269.4903246609786</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29693,10 +29693,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T30" t="n">
         <v>350</v>
@@ -29821,7 +29821,7 @@
         <v>350</v>
       </c>
       <c r="H32" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I32" t="n">
         <v>150.0811596826846</v>
@@ -29854,7 +29854,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T32" t="n">
         <v>350</v>
@@ -29900,7 +29900,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H33" t="n">
-        <v>269.4903246609787</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I33" t="n">
         <v>217.1263858913485</v>
@@ -29945,13 +29945,13 @@
         <v>350</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="X33" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="Y33" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T35" t="n">
         <v>350</v>
@@ -30128,19 +30128,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>325.7395358750273</v>
+        <v>130.1881592409333</v>
       </c>
       <c r="H36" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30179,7 +30179,7 @@
         <v>350</v>
       </c>
       <c r="V36" t="n">
-        <v>279.9943346964701</v>
+        <v>350</v>
       </c>
       <c r="W36" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30328,7 +30328,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T38" t="n">
         <v>350</v>
@@ -30368,10 +30368,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>252.6980156874616</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
         <v>332.1680871864211</v>
@@ -30419,10 +30419,10 @@
         <v>350</v>
       </c>
       <c r="W39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="Y39" t="n">
         <v>350</v>
@@ -30450,19 +30450,19 @@
         <v>350</v>
       </c>
       <c r="G40" t="n">
+        <v>350</v>
+      </c>
+      <c r="H40" t="n">
+        <v>350</v>
+      </c>
+      <c r="I40" t="n">
+        <v>350</v>
+      </c>
+      <c r="J40" t="n">
+        <v>350</v>
+      </c>
+      <c r="K40" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="H40" t="n">
-        <v>350</v>
-      </c>
-      <c r="I40" t="n">
-        <v>350</v>
-      </c>
-      <c r="J40" t="n">
-        <v>350</v>
-      </c>
-      <c r="K40" t="n">
-        <v>350</v>
       </c>
       <c r="L40" t="n">
         <v>350</v>
@@ -30532,10 +30532,10 @@
         <v>350</v>
       </c>
       <c r="H41" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30596,22 +30596,22 @@
         <v>350</v>
       </c>
       <c r="C42" t="n">
-        <v>350</v>
+        <v>276.9584798124343</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>262.1624218828912</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
         <v>217.1263858913485</v>
@@ -30696,7 +30696,7 @@
         <v>350</v>
       </c>
       <c r="J43" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K43" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30760,7 +30760,7 @@
         <v>350</v>
       </c>
       <c r="E44" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="F44" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30848,10 +30848,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>136.6167105523271</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30887,10 +30887,10 @@
         <v>350</v>
       </c>
       <c r="U45" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="V45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -30975,7 +30975,7 @@
         <v>350</v>
       </c>
       <c r="X46" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="Y46" t="n">
         <v>350</v>
@@ -34889,10 +34889,10 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>46.52168149248339</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>36.59397989877566</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -34901,7 +34901,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34934,7 +34934,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
@@ -35114,22 +35114,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>36.59397989877566</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -35138,10 +35138,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
@@ -35183,7 +35183,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>44.57737005009979</v>
       </c>
     </row>
     <row r="8">
@@ -35217,13 +35217,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>385</v>
       </c>
-      <c r="K8" t="n">
-        <v>384.9999999999999</v>
-      </c>
       <c r="L8" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -35232,7 +35232,7 @@
         <v>385</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -35354,31 +35354,31 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>84.46980917586515</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>168.5253324011215</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,13 +35402,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.232467858163426e-11</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
@@ -35417,10 +35417,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35457,10 +35457,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>184.14349316506</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35694,25 +35694,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
+        <v>184.14349316506</v>
+      </c>
+      <c r="L14" t="n">
         <v>559</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
-        <v>257.1230221309867</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>559</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35931,7 +35931,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>184.14349316506</v>
       </c>
       <c r="L17" t="n">
         <v>559</v>
@@ -35940,7 +35940,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>184.1434931650599</v>
+        <v>559</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>136.375834564038</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
         <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -36186,7 +36186,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>20.40522350612654</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
         <v>559</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>141.1524110730752</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O23" t="n">
         <v>559</v>
       </c>
       <c r="P23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36548,7 +36548,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F25" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G25" t="n">
         <v>104.95612715847</v>
@@ -36596,7 +36596,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V25" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W25" t="n">
         <v>123.6271901612903</v>
@@ -36642,25 +36642,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>184.1434931650601</v>
+        <v>300.1141042229713</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36876,13 +36876,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612643</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,13 +36891,13 @@
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37113,16 +37113,16 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>20.40522350612643</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>559</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="L32" t="n">
         <v>559</v>
       </c>
       <c r="M32" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>559</v>
@@ -37134,7 +37134,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37353,25 +37353,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
+        <v>257.1230221309868</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>559</v>
       </c>
-      <c r="L35" t="n">
+      <c r="P35" t="n">
         <v>559</v>
       </c>
-      <c r="M35" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>184.1434931650599</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37587,25 +37587,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>559</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
@@ -37736,7 +37736,7 @@
         <v>75.61714403225807</v>
       </c>
       <c r="G40" t="n">
-        <v>97.1674577926042</v>
+        <v>104.95612715847</v>
       </c>
       <c r="H40" t="n">
         <v>121.2288738983814</v>
@@ -37748,7 +37748,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37824,13 +37824,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>20.40522350612643</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -37845,7 +37845,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J43" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K43" t="n">
         <v>61.47922619885696</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>20.40522350612653</v>
       </c>
       <c r="L44" t="n">
         <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>559</v>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
@@ -38261,7 +38261,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X46" t="n">
-        <v>94.76768520402656</v>
+        <v>102.5563545698924</v>
       </c>
       <c r="Y46" t="n">
         <v>62.53464715053764</v>
